--- a/exam_forms/003_social_emotional_learning_in_the_workplace_test_form--exam_forms.xlsx
+++ b/exam_forms/003_social_emotional_learning_in_the_workplace_test_form--exam_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form</t>
+          <t>intro</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_1</t>
+          <t>experience_anxiety_stress</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -551,10 +551,14 @@
           <t>Have you ever been told that you are too sensitive or overly emotional?</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Describe your experience with anxiety or stress</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,12 +570,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_1_1</t>
+          <t>answer_anxiety_stress_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,20 +588,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_2</t>
+          <t>practice_self_reflection</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How often do you experience feelings of anxiety or stress?</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>How often do you practice self-reflection?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Describe your self-reflection habits</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -612,15 +620,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_2_1</t>
+          <t>set_boundaries</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Do you have difficulty setting boundaries?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Describe any boundary-setting challenges</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -630,23 +642,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_3</t>
+          <t>seek_feedback</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Have you ever experienced feelings of burnout or emotional exhaustion?</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>How often do you seek feedback from others?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Describe your feedback-seeking habits</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,15 +674,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_3_1</t>
+          <t>assert_needs</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Do you have difficulty asserting your needs?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Describe any need-asserting challenges</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>yes</t>
@@ -676,20 +696,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_4</t>
+          <t>engage_self_care</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How often do you practice self-reflection?</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>How often do you engage in activities that promote self-care?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Describe your self-care habits</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
@@ -704,15 +728,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_4_1</t>
+          <t>manage_emotions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Do you have difficulty managing your emotions?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Describe any emotional management challenges</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>yes</t>
@@ -727,18 +755,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_5</t>
+          <t>social_connections</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How often do you engage in activities that promote relaxation?</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>How often do you engage in activities that promote social connections?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Describe your social connection habits</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,15 +782,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_5_1</t>
+          <t>empathize_others</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Do you have difficulty empathizing with others?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Describe any empathizing challenges</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>yes</t>
@@ -773,18 +809,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_6</t>
+          <t>seek_help</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Have you ever experienced difficulty in setting boundaries?</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>How often do you seek help from others when needed?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Describe your help-seeking habits</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,15 +836,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_6_1</t>
+          <t>recognize_emotions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Do you have difficulty recognizing and understanding your emotions?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Describe any emotional recognition challenges</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>yes</t>
@@ -814,20 +858,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_7</t>
+          <t>relax_promote</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How often do you seek feedback from others?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>How often do you engage in activities that promote relaxation?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Describe your relaxation habits</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>yes</t>
@@ -837,253 +885,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_7_1</t>
+          <t>final_questions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Do you have any other comments or concerns?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Describe any other comments or concerns</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_8</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Have you ever experienced difficulty in asserting your needs?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
           <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_8_1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_9</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>How often do you engage in activities that promote self-care?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_9_1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_10</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Have you ever experienced difficulty in managing emotions?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_10_1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_11</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>How often do you engage in activities that promote social connections?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_11_1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_12</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Have you ever experienced difficulty in empathizing with others?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_12_1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,10 +920,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +948,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_1_1_choices</t>
+          <t>answer_anxiety_stress_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +965,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_1_1_choices</t>
+          <t>answer_anxiety_stress_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +982,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_1_1_choices</t>
+          <t>answer_anxiety_stress_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +999,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_1_1_choices</t>
+          <t>answer_anxiety_stress_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +1016,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_2_choices</t>
+          <t>set_boundaries_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1033,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_2_choices</t>
+          <t>set_boundaries_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1050,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_2_choices</t>
+          <t>set_boundaries_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1067,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_2_choices</t>
+          <t>set_boundaries_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1084,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_2_1_choices</t>
+          <t>seek_feedback_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1101,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_2_1_choices</t>
+          <t>seek_feedback_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1118,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_2_1_choices</t>
+          <t>seek_feedback_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1135,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_2_1_choices</t>
+          <t>seek_feedback_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1152,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_3_1_choices</t>
+          <t>assert_needs_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1169,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_3_1_choices</t>
+          <t>assert_needs_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1186,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_3_1_choices</t>
+          <t>assert_needs_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1203,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_3_1_choices</t>
+          <t>assert_needs_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1220,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_4_choices</t>
+          <t>manage_emotions_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1237,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_4_choices</t>
+          <t>manage_emotions_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1254,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_4_choices</t>
+          <t>manage_emotions_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1271,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_4_choices</t>
+          <t>manage_emotions_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,7 +1288,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_4_1_choices</t>
+          <t>empathize_others_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1305,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_4_1_choices</t>
+          <t>empathize_others_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1322,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_4_1_choices</t>
+          <t>empathize_others_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1339,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_4_1_choices</t>
+          <t>empathize_others_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1356,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_5_1_choices</t>
+          <t>recognize_emotions_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1373,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_5_1_choices</t>
+          <t>recognize_emotions_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1390,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_5_1_choices</t>
+          <t>recognize_emotions_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1407,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_5_1_choices</t>
+          <t>recognize_emotions_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1594,550 +1416,6 @@
         </is>
       </c>
       <c r="C29" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_6_1_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>always</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_6_1_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>mostly</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Mostly</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_6_1_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_6_1_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_7_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>always</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_7_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>mostly</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Mostly</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_7_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_question_7_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_7_1_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>always</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_7_1_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>mostly</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Mostly</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_7_1_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_7_1_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_8_1_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>always</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_8_1_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>mostly</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Mostly</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_8_1_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_8_1_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_9_1_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>always</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_9_1_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>mostly</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Mostly</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_9_1_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_9_1_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_10_1_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>always</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_10_1_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>mostly</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Mostly</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_10_1_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_10_1_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_11_1_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>always</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_11_1_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>mostly</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Mostly</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_11_1_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_11_1_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_12_1_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>always</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_12_1_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>mostly</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Mostly</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_12_1_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>social_emotional_learning_in_the_workplace_test_form_answer_12_1_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
         <is>
           <t>Never</t>
         </is>
